--- a/release-package/CrewPay_Ledger_DEMO_PACKAGE/CrewPay_Ledger_Workbook.xlsx
+++ b/release-package/CrewPay_Ledger_DEMO_PACKAGE/CrewPay_Ledger_Workbook.xlsx
@@ -22,7 +22,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin Notices" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar Sync Log" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown Lists" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Config" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending Worker Intake" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending Pay Period Intake" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending Time Entries" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Submission Log" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bridge Schema" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown Lists" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workers'!$A$1:$H$4</definedName>
@@ -37,6 +43,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Schedule'!$A$1:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Admin Notices'!$A$1:$M$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Calendar Sync Log'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'App Config'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Pending Worker Intake'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Pending Pay Period Intake'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Pending Time Entries'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'App Submission Log'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Bridge Schema'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2403,313 +2415,848 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Access Status</t>
+          <t>Config Key</t>
         </is>
       </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
-          <t>Job Status</t>
+          <t>Config Value</t>
         </is>
       </c>
       <c r="C1" s="12" t="inlineStr">
         <is>
-          <t>Approval Status</t>
-        </is>
-      </c>
-      <c r="D1" s="12" t="inlineStr">
-        <is>
-          <t>Pay Period Status</t>
-        </is>
-      </c>
-      <c r="E1" s="12" t="inlineStr">
-        <is>
-          <t>Payment Status</t>
-        </is>
-      </c>
-      <c r="F1" s="12" t="inlineStr">
-        <is>
-          <t>Export Type</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>Schedule Status</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
-        <is>
-          <t>Recipient Type</t>
-        </is>
-      </c>
-      <c r="I1" s="12" t="inlineStr">
-        <is>
-          <t>Delivery Method</t>
-        </is>
-      </c>
-      <c r="J1" s="12" t="inlineStr">
-        <is>
-          <t>Notice Status</t>
-        </is>
-      </c>
-      <c r="K1" s="12" t="inlineStr">
-        <is>
-          <t>Sync Status</t>
-        </is>
-      </c>
-      <c r="M1" s="50" t="inlineStr">
-        <is>
-          <t>Demo Config</t>
-        </is>
-      </c>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Bridge boundary</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="10" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Workbook Source Of Truth</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Unpaid</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="inlineStr">
-        <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="G2" s="14" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t>Worker</t>
-        </is>
-      </c>
-      <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>Workbook</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="K2" s="14" t="inlineStr">
-        <is>
-          <t>Not Synced</t>
-        </is>
-      </c>
-      <c r="M2" s="51" t="inlineStr">
-        <is>
-          <t>Support/config tab for demo dropdowns. Not part of the public workflow.</t>
-        </is>
-      </c>
+          <t>Workbook remains final authority.</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>The workbook remains source of truth. The app may submit controlled intake records through Apps Script after deployment.</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>App Role</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Companion Input Layer</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>All Active Workers</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>Email Ready</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>Posted</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>Synced</t>
-        </is>
-      </c>
+          <t>App submits controlled intake records only.</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n"/>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Backend Type</t>
+        </is>
+      </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Google Apps Script Web App</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>CSV</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>Gmail Sent</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="K4" s="14" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
+          <t>No separate backend server/database.</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n"/>
-      <c r="B5" s="13" t="n"/>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Endpoint URL</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>PASTE_DEPLOYED_APPS_SCRIPT_WEB_APP_URL_HERE</t>
+        </is>
+      </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Finalized</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Canceled</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>Archived</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>Skipped</t>
+          <t>Set after Apps Script deployment.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n"/>
-      <c r="B6" s="14" t="n"/>
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Bridge Enabled</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="n"/>
-      <c r="I6" s="14" t="n"/>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="14" t="n"/>
+          <t>Turn TRUE only after deployment/testing.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n"/>
-      <c r="B7" s="13" t="n"/>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Shared Token Required</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
+          <t>Browser-visible token is not full security; use private/demo boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Intake Review Required</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>App submissions should be reviewed before final record use.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
+  <mergeCells count="2">
+    <mergeCell ref="E2:H4"/>
+    <mergeCell ref="E1:H1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose a value from Dropdown Lists." type="list">
+      <formula1>'Dropdown Lists'!$M$2:$M$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6:B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose a value from Dropdown Lists." type="list">
+      <formula1>'Dropdown Lists'!$M$2:$M$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Intake ID</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Submitted At</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Submission Source</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Submission Status</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Worker ID</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Worker Name</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Access Status</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Role / Trade</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>Reviewed At</t>
+        </is>
+      </c>
+      <c r="L1" s="12" t="inlineStr">
+        <is>
+          <t>Reviewed By</t>
+        </is>
+      </c>
+      <c r="M1" s="12" t="inlineStr">
+        <is>
+          <t>Review Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>PW-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n">
+        <v>46183.375</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>App Demo</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>W-001</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Sample Worker</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Crew</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>sample@example.com</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>Sample pending worker intake row.</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr"/>
+      <c r="L2" s="14" t="inlineStr"/>
+      <c r="M2" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M2"/>
+  <conditionalFormatting sqref="A2:M200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$D2="Active"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$D2="Approved"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>$D2="Paid"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>$D2="Submitted"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="2">
+      <formula>$D2="Draft"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>$D2="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>$D2="Posted"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>$D2="Email Ready"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>$D2="Scheduled"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>$D2="Planned"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="3">
+      <formula>$D2="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="4">
+      <formula>$D2="Inactive"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="4">
+      <formula>$D2="Archived"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="4">
+      <formula>$D2="Closed"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="4">
+      <formula>$D2="Canceled"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="4">
+      <formula>$D2="Cancelled"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose a value from Dropdown Lists." type="list">
+      <formula1>'Dropdown Lists'!$L$2:$L$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose a value from Dropdown Lists." type="list">
+      <formula1>'Dropdown Lists'!$A$2:$A$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Intake ID</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Submitted At</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Submission Source</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Submission Status</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Pay Period ID</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Worker ID</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Worker Name</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Period Start</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Period End</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Pay Date</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="L1" s="12" t="inlineStr">
+        <is>
+          <t>Reviewed At</t>
+        </is>
+      </c>
+      <c r="M1" s="12" t="inlineStr">
+        <is>
+          <t>Reviewed By</t>
+        </is>
+      </c>
+      <c r="N1" s="12" t="inlineStr">
+        <is>
+          <t>Review Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>PP-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n">
+        <v>46183.37847222222</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>App Demo</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>PP-001</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>W-001</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Sample Worker</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>46174</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>46180</v>
+      </c>
+      <c r="J2" s="15" t="n">
+        <v>46187</v>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>Sample pending pay period row.</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr"/>
+      <c r="M2" s="14" t="inlineStr"/>
+      <c r="N2" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N2"/>
+  <conditionalFormatting sqref="A2:N200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$D2="Active"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$D2="Approved"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>$D2="Paid"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>$D2="Submitted"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="2">
+      <formula>$D2="Draft"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>$D2="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>$D2="Posted"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>$D2="Email Ready"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>$D2="Scheduled"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>$D2="Planned"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="3">
+      <formula>$D2="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="4">
+      <formula>$D2="Inactive"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="4">
+      <formula>$D2="Archived"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="4">
+      <formula>$D2="Closed"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="4">
+      <formula>$D2="Canceled"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="4">
+      <formula>$D2="Cancelled"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose a value from Dropdown Lists." type="list">
+      <formula1>'Dropdown Lists'!$L$2:$L$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="36" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Intake ID</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Submitted At</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Submission Source</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Submission Status</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Entry ID</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Worker ID</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Worker Name</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Pay Period ID</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Work Date</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Job / Work Type</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="L1" s="12" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="M1" s="12" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="N1" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="O1" s="12" t="inlineStr">
+        <is>
+          <t>Reviewed At</t>
+        </is>
+      </c>
+      <c r="P1" s="12" t="inlineStr">
+        <is>
+          <t>Reviewed By</t>
+        </is>
+      </c>
+      <c r="Q1" s="12" t="inlineStr">
+        <is>
+          <t>Review Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>PT-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n">
+        <v>46183.38194444445</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>App Demo</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>E-001</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>W-001</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Sample Worker</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>PP-001</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>Sample Work</t>
+        </is>
+      </c>
+      <c r="K2" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="M2" s="17">
+        <f>K2*L2</f>
+        <v/>
+      </c>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>Sample pending time entry row.</t>
+        </is>
+      </c>
+      <c r="O2" s="14" t="inlineStr"/>
+      <c r="P2" s="14" t="inlineStr"/>
+      <c r="Q2" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q2"/>
+  <conditionalFormatting sqref="A2:Q200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$D2="Active"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$D2="Approved"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>$D2="Paid"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>$D2="Submitted"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="2">
+      <formula>$D2="Draft"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>$D2="Finalized"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>$D2="Posted"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>$D2="Email Ready"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>$D2="Scheduled"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>$D2="Planned"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="3">
+      <formula>$D2="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="4">
+      <formula>$D2="Inactive"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" dxfId="4">
+      <formula>$D2="Archived"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="4">
+      <formula>$D2="Closed"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="4">
+      <formula>$D2="Canceled"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="4">
+      <formula>$D2="Cancelled"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Choose a value from Dropdown Lists." type="list">
+      <formula1>'Dropdown Lists'!$L$2:$L$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3013,6 +3560,893 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="G9:H9"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Log ID</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Submitted At</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Submission Source</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Related Intake ID</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Related Worker ID</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Related Pay Period ID</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Raw Payload Summary</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>Handled By Script Version</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>AL-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n">
+        <v>46183.38541666666</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>healthCheck</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>App Demo</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr"/>
+      <c r="G2" s="14" t="inlineStr"/>
+      <c r="H2" s="14" t="inlineStr"/>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>Sample app submission log row.</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>Sample only.</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>Not deployed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Target Tab</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Required Fields</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Optional Fields</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Success Response</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Error Conditions</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>healthCheck</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>App Submission Log</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>client_version, submission_source</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>{ok:true, action:"healthCheck", workbook:"CrewPay Ledger"}</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Bridge disabled; workbook unavailable</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Readiness check only; may log a health check row if desired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>getWorkbookSchema</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Bridge Schema / Dropdown Lists</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>{ok:true, config:{...}, dropdowns:{...}}</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Bridge disabled; schema unavailable</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Return allowed tabs, writable fields, and dropdown values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>submitWorkerIntake</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Pending Worker Intake</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>worker_name, access_status, role_trade, contact</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>worker_id, notes, idempotency_key</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>{ok:true, intake_id:'PW-####'}</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Missing required field; duplicate submission; invalid access status</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>First landing zone for worker records from the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>submitPayPeriod</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Pending Pay Period Intake</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>pay_period_id, worker_id, period_start, period_end</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>worker_name, pay_date, notes, idempotency_key</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>{ok:true, intake_id:'PP-####'}</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Invalid date range; missing worker; duplicate submission</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Pending setup only. Final Pay Periods tab remains workbook/admin reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>submitTimeEntry</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Pending Time Entries</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>worker_id, pay_period_id, work_date, job_work_type, hours, rate</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>worker_name, entry_id, notes, idempotency_key</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>{ok:true, intake_id:'PT-####'}</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Inactive worker; invalid hours/rate; duplicate submission</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Safest first write target for app time entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>logProofExport</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Proof Exports</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>worker_id, pay_period_id, export_type, export_reference</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>worker_name, notes</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>{ok:true, export_id:'X-####'}</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Worker/pay period mismatch; invalid export type</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Do not write Worker Proof directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>logCorrection</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Correction Log</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>entry_id, worker_id, pay_period_id, correction_reason, original_value_summary, new_value_summary</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>worker_name, notes</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>{ok:true, correction_id:'C-####'}</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Missing proof context; duplicate correction</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Corrections must be visible, not silent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>logAccessChange</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Access Log</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>worker_id, previous_status, new_status, reason</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>worker_name</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>{ok:true, log_id:'A-####'}</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Invalid status; missing reason</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Future access changes must preserve historical proof.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>createAdminNotice</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Admin Notices</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>recipient_type, subject, message</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>worker_id, worker_name, related_pay_period_id, notes</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>{ok:true, notice_id:'N-####'}</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Invalid recipient type; missing message</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Creates a one-way notice row only; sending is separate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Access Status</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Job Status</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Approval Status</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Pay Period Status</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Payment Status</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Export Type</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Schedule Status</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Recipient Type</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Delivery Method</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Notice Status</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>Sync Status</t>
+        </is>
+      </c>
+      <c r="L1" s="12" t="inlineStr">
+        <is>
+          <t>Submission Status</t>
+        </is>
+      </c>
+      <c r="M1" s="12" t="inlineStr">
+        <is>
+          <t>Boolean Flag</t>
+        </is>
+      </c>
+      <c r="O1" s="50" t="inlineStr">
+        <is>
+          <t>Demo Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>Not Synced</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O2" s="51" t="inlineStr">
+        <is>
+          <t>Support/config tab for demo dropdowns. Not part of the public workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Paused</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>All Active Workers</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>Email Ready</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Synced</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n"/>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Gmail Sent</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Canceled</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Archived</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n"/>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
